--- a/output/pdf_financials_xlsx/XXIX.xlsx
+++ b/output/pdf_financials_xlsx/XXIX.xlsx
@@ -3132,25 +3132,25 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.346262</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.630881</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.659304</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.823722</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>3.169209</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.662277</v>
       </c>
     </row>
     <row r="93">
@@ -5257,7 +5257,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -5951,7 +5955,11 @@
           <t>Reserves 10, 11</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -6247,7 +6255,11 @@
           <t>Reserves 11, 12</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -7122,7 +7134,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>0.346262</v>
       </c>

--- a/output/pdf_financials_xlsx/XXIX.xlsx
+++ b/output/pdf_financials_xlsx/XXIX.xlsx
@@ -693,25 +693,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.16685</v>
+        <v>1.111603</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.3381</v>
+        <v>1.243009</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.377879</v>
+        <v>0.181875</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.363137</v>
+        <v>10.361079</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.380405</v>
+        <v>4.977949</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.167215</v>
+        <v>2.91248</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.381145</v>
+        <v>17.741859</v>
       </c>
     </row>
     <row r="11">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.16685</v>
+        <v>-1.111603</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.3381</v>
+        <v>-1.243009</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.149131</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.301635</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.231777</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.127563</v>
       </c>
     </row>
     <row r="13">
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-4.857132</v>
+        <v>-4.625355</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-15.728001</v>
+        <v>-15.600438</v>
       </c>
     </row>
     <row r="28">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.857132</v>
+        <v>-4.625355</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-15.728001</v>
+        <v>-15.600438</v>
       </c>
     </row>
     <row r="30">
@@ -1452,25 +1452,25 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.500337</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.346851</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>17.508624</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>8.855598000000001</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>5.77039</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>4.062643</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>6.40994</v>
       </c>
     </row>
     <row r="35">
@@ -1508,25 +1508,25 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.500337</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.346851</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>17.508624</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>8.855598000000001</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>5.77039</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>4.062643</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>6.40994</v>
       </c>
     </row>
     <row r="37">
@@ -1844,25 +1844,25 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.521797</v>
+        <v>0.02146</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.443423</v>
+        <v>0.09657200000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>17.632045</v>
+        <v>0.123421</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>15.557229</v>
+        <v>6.701631</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>10.484347</v>
+        <v>4.713957</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>6.607456</v>
+        <v>2.544813</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>8.113125999999999</v>
+        <v>1.703186</v>
       </c>
     </row>
     <row r="49">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -12621,7 +12621,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -13717,7 +13717,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -14580,7 +14580,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E203" s="5" t="n">

--- a/output/pdf_financials_xlsx/XXIX.xlsx
+++ b/output/pdf_financials_xlsx/XXIX.xlsx
@@ -911,7 +911,7 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.03</v>
+        <v>-0.058</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.019372</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>0</v>
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.01317</v>
+        <v>-0.006202</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.029801</v>
@@ -3639,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.048448</v>
       </c>
     </row>
     <row r="111">
@@ -3655,7 +3655,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.051708</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -3667,7 +3667,7 @@
         <v>-0.120583</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.166736</v>
       </c>
     </row>
     <row r="112">
@@ -3845,7 +3845,7 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>0.388988</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.051708</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -4331,7 +4331,7 @@
         <v>-0.120583</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.166736</v>
       </c>
     </row>
     <row r="135">
@@ -4365,7 +4365,7 @@
         <v>-1.707747</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-3.47109</v>
+        <v>-3.637826</v>
       </c>
     </row>
   </sheetData>
@@ -4379,7 +4379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K208"/>
+  <dimension ref="A1:K221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7901,7 +7901,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -8534,7 +8538,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -11247,20 +11255,26 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital items</t>
+        </is>
+      </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>For the years ended Notes October 31, 2025 October</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GST/HST receivable</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>-0.019372</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11282,34 +11296,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J137" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="K137" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures 5,10,14</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Exploration and evaluation asset expenditures</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>-0.051012</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11331,38 +11351,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J138" s="5" t="n">
-        <v>1.309554</v>
-      </c>
-      <c r="K138" s="5" t="n">
-        <v>15.655116</v>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder communications</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Advances to Orefinders Resources Inc.</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" s="5" t="n">
+        <v>-0.01016</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11384,34 +11402,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J139" s="5" t="n">
-        <v>0.167215</v>
-      </c>
-      <c r="K139" s="5" t="n">
-        <v>0.381145</v>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Management and consulting 14</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="n">
+        <v>-0.061172</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11433,38 +11457,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J140" s="5" t="n">
-        <v>0.532395</v>
-      </c>
-      <c r="K140" s="5" t="n">
-        <v>0.669463</v>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Issuance of common shares</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11486,34 +11512,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J141" s="5" t="n">
-        <v>0.2654</v>
-      </c>
-      <c r="K141" s="5" t="n">
-        <v>0.187457</v>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Share-based compensation 13</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net Increase in Cash</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="n">
+        <v>0.500337</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11535,32 +11567,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J142" s="5" t="n">
-        <v>0.415487</v>
-      </c>
-      <c r="K142" s="5" t="n">
-        <v>0.598892</v>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Office, general and administrative</t>
+          <t>Cash, Beginning of Period</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -11588,38 +11624,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J143" s="5" t="n">
-        <v>0.210554</v>
-      </c>
-      <c r="K143" s="5" t="n">
-        <v>0.15701</v>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Amortization 9</t>
+          <t>Cash, End of Period $</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="n">
+        <v>0.500337</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -11641,34 +11679,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J144" s="5" t="n">
-        <v>0.011875</v>
-      </c>
-      <c r="K144" s="5" t="n">
-        <v>0.044328</v>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder</t>
+          <t>Supplemental Information</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Accretion expense</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Shares issued for exploration and evaluation assets $</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="n">
+        <v>0.44</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -11695,35 +11739,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K145" s="5" t="n">
-        <v>0.048448</v>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder</t>
+          <t>Supplemental Information</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>TOTAL EXPENSES</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Finders’ warrants issued $</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" s="5" t="n">
+        <v>0.004</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -11745,34 +11785,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J146" s="5" t="n">
-        <v>2.91248</v>
-      </c>
-      <c r="K146" s="5" t="n">
-        <v>17.741859</v>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder</t>
+          <t>Supplemental Information</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Unrealized loss on investment 7</t>
+          <t>Warrants issued under plan of arrangement $</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E147" s="5" t="n">
+        <v>0.015</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -11794,11 +11836,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J147" s="5" t="n">
-        <v>2.176429</v>
-      </c>
-      <c r="K147" s="5" t="n">
-        <v>0.239264</v>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -11807,14 +11853,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Transfer agent, filing fees and shareholder</t>
-        </is>
-      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Loss from associate 8</t>
+          <t>For the years ended Notes October 31, 2025 October</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -11843,13 +11885,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J148" s="5" t="n">
+        <v>0.002024</v>
       </c>
       <c r="K148" s="5" t="n">
-        <v>0.016191</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="149">
@@ -11860,12 +11900,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>(Gain) on disposition of Roger Project 8,15</t>
+          <t>Exploration and evaluation expenditures 5,10,14</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -11894,13 +11934,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J149" s="5" t="n">
+        <v>1.309554</v>
       </c>
       <c r="K149" s="5" t="n">
-        <v>-1.92375</v>
+        <v>15.655116</v>
       </c>
     </row>
     <row r="150">
@@ -11916,18 +11954,16 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Transfer agent, filing fees and shareholder communications</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="n">
+        <v>0.131606</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11950,10 +11986,10 @@
         </is>
       </c>
       <c r="J150" s="5" t="n">
-        <v>-0.231777</v>
+        <v>0.167215</v>
       </c>
       <c r="K150" s="5" t="n">
-        <v>-0.127563</v>
+        <v>0.381145</v>
       </c>
     </row>
     <row r="151">
@@ -11969,14 +12005,10 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Loss (income) from continuing operations</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>NetIncomeContinuousOperations</t>
-        </is>
-      </c>
+          <t>Management and consulting 14</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -12003,10 +12035,10 @@
         </is>
       </c>
       <c r="J151" s="5" t="n">
-        <v>4.857132</v>
+        <v>0.532395</v>
       </c>
       <c r="K151" s="5" t="n">
-        <v>15.946001</v>
+        <v>0.669463</v>
       </c>
     </row>
     <row r="152">
@@ -12017,15 +12049,19 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>Transfer agent, filing fees and shareholder</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Flow-through share premium liability recovery</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -12051,13 +12087,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J152" s="5" t="n">
+        <v>0.2654</v>
       </c>
       <c r="K152" s="5" t="n">
-        <v>-0.218</v>
+        <v>0.187457</v>
       </c>
     </row>
     <row r="153">
@@ -12068,12 +12102,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>NET (LOSS) AND COMPREHENSIVE (LOSS) FOR</t>
+          <t>Transfer agent, filing fees and shareholder</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>THE YEAR</t>
+          <t>Share-based compensation 13</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -12103,10 +12137,10 @@
         </is>
       </c>
       <c r="J153" s="5" t="n">
-        <v>-4.857132</v>
+        <v>0.415487</v>
       </c>
       <c r="K153" s="5" t="n">
-        <v>-15.728001</v>
+        <v>0.598892</v>
       </c>
     </row>
     <row r="154">
@@ -12117,15 +12151,19 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Weighted average number of shares - basic and</t>
+          <t>Transfer agent, filing fees and shareholder</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Weighted average number of shares - basic and diluted</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
+          <t>Office, general and administrative</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -12152,10 +12190,10 @@
         </is>
       </c>
       <c r="J154" s="5" t="n">
-        <v>173.879219</v>
+        <v>0.210554</v>
       </c>
       <c r="K154" s="5" t="n">
-        <v>259.331194</v>
+        <v>0.15701</v>
       </c>
     </row>
     <row r="155">
@@ -12166,17 +12204,17 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Weighted average number of shares - basic and</t>
+          <t>Transfer agent, filing fees and shareholder</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>(Loss) per share – basic and diluted $</t>
+          <t>Amortization 9</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -12205,10 +12243,10 @@
         </is>
       </c>
       <c r="J155" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.011875</v>
       </c>
       <c r="K155" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>0.044328</v>
       </c>
     </row>
     <row r="156">
@@ -12219,12 +12257,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Transfer agent, filing fees and shareholder</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Exploration expense 6, 10,11</t>
+          <t>Accretion expense</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
@@ -12248,16 +12286,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I156" s="5" t="n">
-        <v>4.002725</v>
-      </c>
-      <c r="J156" s="5" t="n">
-        <v>1.309554</v>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>0.048448</v>
       </c>
     </row>
     <row r="157">
@@ -12268,17 +12308,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Transfer agent, filing fees and shareholder</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Consulting, wages and management fees 11</t>
+          <t>TOTAL EXPENSES</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -12301,16 +12341,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="5" t="n">
-        <v>0.380405</v>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J157" s="5" t="n">
-        <v>0.532395</v>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.91248</v>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>17.741859</v>
       </c>
     </row>
     <row r="158">
@@ -12321,19 +12361,15 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Transfer agent, filing fees and shareholder</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Unrealized loss on investment 7</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -12344,22 +12380,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G158" s="5" t="n">
-        <v>0.338929</v>
-      </c>
-      <c r="H158" s="5" t="n">
-        <v>0.331283</v>
-      </c>
-      <c r="I158" s="5" t="n">
-        <v>0.121463</v>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J158" s="5" t="n">
-        <v>0.2654</v>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.176429</v>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>0.239264</v>
       </c>
     </row>
     <row r="159">
@@ -12375,7 +12415,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder total</t>
+          <t>Loss from associate 8</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
@@ -12394,19 +12434,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H159" s="5" t="n">
-        <v>0.320264</v>
-      </c>
-      <c r="I159" s="5" t="n">
-        <v>0.155791</v>
-      </c>
-      <c r="J159" s="5" t="n">
-        <v>0.167215</v>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>0.016191</v>
       </c>
     </row>
     <row r="160">
@@ -12417,12 +12461,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>communications</t>
+          <t>Transfer agent, filing fees and shareholder</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Travel and related costs</t>
+          <t>(Gain) on disposition of Roger Project 8,15</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -12441,19 +12485,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H160" s="5" t="n">
-        <v>0.051629</v>
-      </c>
-      <c r="I160" s="5" t="n">
-        <v>0.028167</v>
-      </c>
-      <c r="J160" s="5" t="n">
-        <v>0.083422</v>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>-1.92375</v>
       </c>
     </row>
     <row r="161">
@@ -12464,15 +12512,19 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>communications</t>
+          <t>Transfer agent, filing fees and shareholder</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Office, rent and general</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -12488,19 +12540,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H161" s="5" t="n">
-        <v>0.094953</v>
-      </c>
-      <c r="I161" s="5" t="n">
-        <v>0.131764</v>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J161" s="5" t="n">
-        <v>0.127132</v>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.231777</v>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>-0.127563</v>
       </c>
     </row>
     <row r="162">
@@ -12511,17 +12565,17 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>communications</t>
+          <t>Transfer agent, filing fees and shareholder</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Amortization 5</t>
+          <t>Loss (income) from continuing operations</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>NetIncomeContinuousOperations</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -12539,19 +12593,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H162" s="5" t="n">
-        <v>0.015494</v>
-      </c>
-      <c r="I162" s="5" t="n">
-        <v>0.011107</v>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J162" s="5" t="n">
-        <v>0.011875</v>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.857132</v>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>15.946001</v>
       </c>
     </row>
     <row r="163">
@@ -12562,12 +12618,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>communications</t>
+          <t>Deferred income tax recovery</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Share-based payments 10,11</t>
+          <t>Flow-through share premium liability recovery</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
@@ -12591,16 +12647,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I163" s="5" t="n">
-        <v>0.146527</v>
-      </c>
-      <c r="J163" s="5" t="n">
-        <v>0.415487</v>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>-0.218</v>
       </c>
     </row>
     <row r="164">
@@ -12611,19 +12669,15 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>communications</t>
+          <t>NET (LOSS) AND COMPREHENSIVE (LOSS) FOR</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TOTAL EXPENSES</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>THE YEAR</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -12639,19 +12693,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H164" s="5" t="n">
-        <v>10.361079</v>
-      </c>
-      <c r="I164" s="5" t="n">
-        <v>4.977949</v>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J164" s="5" t="n">
-        <v>2.91248</v>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.857132</v>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>-15.728001</v>
       </c>
     </row>
     <row r="165">
@@ -12662,12 +12718,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>communications</t>
+          <t>Weighted average number of shares - basic and</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Unrealized loss on investment 7</t>
+          <t>Weighted average number of shares - basic and diluted</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -12691,16 +12747,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I165" s="5" t="n">
-        <v>2.645908</v>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J165" s="5" t="n">
-        <v>2.176429</v>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>173.879219</v>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>259.331194</v>
       </c>
     </row>
     <row r="166">
@@ -12711,17 +12767,17 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>communications</t>
+          <t>Weighted average number of shares - basic and</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>(Loss) per share – basic and diluted $</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -12739,19 +12795,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H166" s="5" t="n">
-        <v>-0.149131</v>
-      </c>
-      <c r="I166" s="5" t="n">
-        <v>-0.301635</v>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J166" s="5" t="n">
-        <v>-0.231777</v>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3e-08</v>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
       </c>
     </row>
     <row r="167">
@@ -12762,12 +12820,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>communications</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Loss before tax</t>
+          <t>Exploration expense 6, 10,11</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -12786,14 +12844,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H167" s="5" t="n">
-        <v>6.519941</v>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I167" s="5" t="n">
-        <v>7.322222</v>
+        <v>4.002725</v>
       </c>
       <c r="J167" s="5" t="n">
-        <v>4.857132</v>
+        <v>1.309554</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
@@ -12809,15 +12869,19 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>NET LOSS AND COMPREHENSIVE LOSS FOR</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>NET LOSS AND COMPREHENSIVE LOSS FOR total</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
+          <t>Consulting, wages and management fees 11</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -12833,14 +12897,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H168" s="5" t="n">
-        <v>3.906388</v>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I168" s="5" t="n">
-        <v>7.322222</v>
+        <v>0.380405</v>
       </c>
       <c r="J168" s="5" t="n">
-        <v>4.857132</v>
+        <v>0.532395</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -12856,17 +12922,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Weighted average number of shares - basic</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Weighted average number of shares - basic total</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -12879,19 +12945,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G169" s="5" t="n">
+        <v>0.338929</v>
       </c>
       <c r="H169" s="5" t="n">
-        <v>146.238517</v>
+        <v>0.331283</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>161.97621</v>
+        <v>0.121463</v>
       </c>
       <c r="J169" s="5" t="n">
-        <v>173.879219</v>
+        <v>0.2654</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -12907,23 +12971,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>and diluted</t>
+          <t>Transfer agent, filing fees and shareholder</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Transfer agent, filing fees and shareholder total</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" s="5" t="n">
+        <v>0.605591</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -12936,13 +12994,13 @@
         </is>
       </c>
       <c r="H170" s="5" t="n">
-        <v>3e-08</v>
+        <v>0.320264</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>-5e-08</v>
+        <v>0.155791</v>
       </c>
       <c r="J170" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.167215</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
@@ -12958,12 +13016,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>communications</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Exploration expense 6,12</t>
+          <t>Travel and related costs</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -12977,19 +13035,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G171" s="5" t="n">
-        <v>6.225093</v>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H171" s="5" t="n">
-        <v>8.269693999999999</v>
+        <v>0.051629</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>4.002725</v>
-      </c>
-      <c r="J171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.028167</v>
+      </c>
+      <c r="J171" s="5" t="n">
+        <v>0.083422</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -13005,19 +13063,15 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>communications</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Consulting, wages and management fees 12</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Office, rent and general</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -13028,19 +13082,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G172" s="5" t="n">
-        <v>0.377879</v>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H172" s="5" t="n">
-        <v>0.363137</v>
+        <v>0.094953</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>0.380405</v>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.131764</v>
+      </c>
+      <c r="J172" s="5" t="n">
+        <v>0.127132</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -13061,10 +13115,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Share-based payments 11,12</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>Amortization 5</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -13081,15 +13139,13 @@
         </is>
       </c>
       <c r="H173" s="5" t="n">
-        <v>0.914625</v>
+        <v>0.015494</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>0.146527</v>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.011107</v>
+      </c>
+      <c r="J173" s="5" t="n">
+        <v>0.011875</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -13110,7 +13166,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Equity loss on investment in associate</t>
+          <t>Share-based payments 10,11</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -13129,18 +13185,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H174" s="5" t="n">
-        <v>0.190008</v>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="5" t="n">
+        <v>0.146527</v>
+      </c>
+      <c r="J174" s="5" t="n">
+        <v>0.415487</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -13161,10 +13215,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Unrealized loss (gain) on investment 7</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
+          <t>TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -13181,15 +13239,13 @@
         </is>
       </c>
       <c r="H175" s="5" t="n">
-        <v>-2.678989</v>
+        <v>10.361079</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>2.645908</v>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.977949</v>
+      </c>
+      <c r="J175" s="5" t="n">
+        <v>2.91248</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
@@ -13210,7 +13266,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>(Gain) on dilution of investment in associate 7</t>
+          <t>Unrealized loss on investment 7</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -13229,18 +13285,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H176" s="5" t="n">
-        <v>-1.203026</v>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" s="5" t="n">
+        <v>2.645908</v>
+      </c>
+      <c r="J176" s="5" t="n">
+        <v>2.176429</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -13256,15 +13310,19 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>communications</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Flow-through share premium liability renunciation 10,13,14</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -13281,17 +13339,13 @@
         </is>
       </c>
       <c r="H177" s="5" t="n">
-        <v>2.613553</v>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.149131</v>
+      </c>
+      <c r="I177" s="5" t="n">
+        <v>-0.301635</v>
+      </c>
+      <c r="J177" s="5" t="n">
+        <v>-0.231777</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
@@ -13307,12 +13361,12 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>communications</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Travel and related costs</t>
+          <t>Loss before tax</t>
         </is>
       </c>
       <c r="D178" t="inlineStr"/>
@@ -13326,21 +13380,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G178" s="5" t="n">
-        <v>0.021285</v>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H178" s="5" t="n">
-        <v>0.051629</v>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.519941</v>
+      </c>
+      <c r="I178" s="5" t="n">
+        <v>7.322222</v>
+      </c>
+      <c r="J178" s="5" t="n">
+        <v>4.857132</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -13356,12 +13408,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>NET LOSS AND COMPREHENSIVE LOSS FOR</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Office, rent and general (recovery)</t>
+          <t>NET LOSS AND COMPREHENSIVE LOSS FOR total</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -13375,21 +13427,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G179" s="5" t="n">
-        <v>0.023141</v>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H179" s="5" t="n">
-        <v>-0.054178</v>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.906388</v>
+      </c>
+      <c r="I179" s="5" t="n">
+        <v>7.322222</v>
+      </c>
+      <c r="J179" s="5" t="n">
+        <v>4.857132</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -13405,17 +13455,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Weighted average number of shares - basic</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Amortization 5</t>
+          <t>Weighted average number of shares - basic total</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -13428,21 +13478,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G180" s="5" t="n">
-        <v>0.011883</v>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H180" s="5" t="n">
-        <v>0.015494</v>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>146.238517</v>
+      </c>
+      <c r="I180" s="5" t="n">
+        <v>161.97621</v>
+      </c>
+      <c r="J180" s="5" t="n">
+        <v>173.879219</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -13458,15 +13506,19 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>and diluted</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Share-based payments 11,12</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>Loss per share – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -13477,21 +13529,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G181" s="5" t="n">
-        <v>0.079176</v>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H181" s="5" t="n">
-        <v>0.914625</v>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3e-08</v>
+      </c>
+      <c r="I181" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="J181" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -13512,7 +13562,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Equity loss on investment in associate 7</t>
+          <t>Exploration expense 6,12</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -13527,15 +13577,13 @@
         </is>
       </c>
       <c r="G182" s="5" t="n">
-        <v>1.762423</v>
+        <v>6.225093</v>
       </c>
       <c r="H182" s="5" t="n">
-        <v>0.190008</v>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.269693999999999</v>
+      </c>
+      <c r="I182" s="5" t="n">
+        <v>4.002725</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -13561,10 +13609,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Gain on sale of shares of associate 7</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
+          <t>Consulting, wages and management fees 12</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -13576,17 +13628,13 @@
         </is>
       </c>
       <c r="G183" s="5" t="n">
-        <v>-5.987299</v>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.377879</v>
+      </c>
+      <c r="H183" s="5" t="n">
+        <v>0.363137</v>
+      </c>
+      <c r="I183" s="5" t="n">
+        <v>0.380405</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -13607,12 +13655,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>communications</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Unrealized gain on investment 7</t>
+          <t>Share-based payments 11,12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -13632,12 +13680,10 @@
         </is>
       </c>
       <c r="H184" s="5" t="n">
-        <v>-2.678989</v>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.914625</v>
+      </c>
+      <c r="I184" s="5" t="n">
+        <v>0.146527</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -13658,12 +13704,12 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>communications</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Gain on dilution of investment in associate 7</t>
+          <t>Equity loss on investment in associate</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -13677,11 +13723,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G185" s="5" t="n">
-        <v>-3.085003</v>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H185" s="5" t="n">
-        <v>-1.203026</v>
+        <v>0.190008</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -13707,19 +13755,15 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>communications</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>TOTAL EXPENSES</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Unrealized loss (gain) on investment 7</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -13730,16 +13774,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G186" s="5" t="n">
-        <v>0.181875</v>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H186" s="5" t="n">
-        <v>6.519941</v>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.678989</v>
+      </c>
+      <c r="I186" s="5" t="n">
+        <v>2.645908</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -13760,12 +13804,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>communications</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Loss from operations for the year</t>
+          <t>(Gain) on dilution of investment in associate 7</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -13779,11 +13823,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G187" s="5" t="n">
-        <v>0.181875</v>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H187" s="5" t="n">
-        <v>6.519941</v>
+        <v>-1.203026</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -13809,7 +13855,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense)</t>
+          <t>Deferred income tax recovery</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -13828,8 +13874,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G188" s="5" t="n">
-        <v>0.636</v>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H188" s="5" t="n">
         <v>2.613553</v>
@@ -13858,12 +13906,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery 13</t>
+          <t>Travel and related costs</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -13878,12 +13926,10 @@
         </is>
       </c>
       <c r="G189" s="5" t="n">
-        <v>0.058</v>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.021285</v>
+      </c>
+      <c r="H189" s="5" t="n">
+        <v>0.051629</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -13909,19 +13955,15 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Income tax recovery (expense)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Current income tax expense 13</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>Office, rent and general (recovery)</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -13933,12 +13975,10 @@
         </is>
       </c>
       <c r="G190" s="5" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.023141</v>
+      </c>
+      <c r="H190" s="5" t="n">
+        <v>-0.054178</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -13964,17 +14004,17 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>$3,906,388          $(482,125)    LOSS (INCOME) FOR THE YEAR</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Weighted average number of shares - basic</t>
+          <t>Amortization 5</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>BasicAverageShares</t>
+          <t>Amortization</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -13988,10 +14028,10 @@
         </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>110.224168</v>
+        <v>0.011883</v>
       </c>
       <c r="H191" s="5" t="n">
-        <v>146.238517</v>
+        <v>0.015494</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -14017,19 +14057,15 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Loss (earnings) per share – basic                                      $0.03              $(0.01)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Weighted average number of shares - diluted</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>DilutedAverageShares</t>
-        </is>
-      </c>
+          <t>Share-based payments 11,12</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -14041,10 +14077,10 @@
         </is>
       </c>
       <c r="G192" s="5" t="n">
-        <v>124.350126</v>
+        <v>0.079176</v>
       </c>
       <c r="H192" s="5" t="n">
-        <v>146.238517</v>
+        <v>0.914625</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -14070,30 +14106,30 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Period from</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>February</t>
+          <t>Equity loss on investment in associate 7</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
-      <c r="E193" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F193" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G193" s="5" t="n">
+        <v>1.762423</v>
+      </c>
+      <c r="H193" s="5" t="n">
+        <v>0.190008</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -14119,25 +14155,27 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>(date of</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Notes October 31, 2019 October</t>
+          <t>Gain on sale of shares of associate 7</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
-      <c r="E194" s="5" t="n">
-        <v>0.002018</v>
-      </c>
-      <c r="F194" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G194" s="5" t="n">
+        <v>-5.987299</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -14168,34 +14206,32 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Consulting and management fees 10 $</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E195" s="5" t="n">
-        <v>0.16685</v>
-      </c>
-      <c r="F195" s="5" t="n">
-        <v>0.3381</v>
+          <t>Unrealized gain on investment 7</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H195" s="5" t="n">
+        <v>-2.678989</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -14221,30 +14257,30 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Exploration expense 5,10,14</t>
+          <t>Gain on dilution of investment in associate 7</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
-      <c r="E196" s="5" t="n">
-        <v>0.506012</v>
-      </c>
-      <c r="F196" s="5" t="n">
-        <v>0.532691</v>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G196" s="5" t="n">
+        <v>-3.085003</v>
+      </c>
+      <c r="H196" s="5" t="n">
+        <v>-1.203026</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -14270,30 +14306,34 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Share-based payments 9</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" s="5" t="n">
-        <v>0.182262</v>
-      </c>
-      <c r="F197" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G197" s="5" t="n">
+        <v>0.181875</v>
+      </c>
+      <c r="H197" s="5" t="n">
+        <v>6.519941</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -14319,30 +14359,30 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Office, rent and general</t>
+          <t>Loss from operations for the year</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
-      <c r="E198" s="5" t="n">
-        <v>0.00471</v>
-      </c>
-      <c r="F198" s="5" t="n">
-        <v>0.041904</v>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G198" s="5" t="n">
+        <v>0.181875</v>
+      </c>
+      <c r="H198" s="5" t="n">
+        <v>6.519941</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -14368,34 +14408,30 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income tax recovery (expense)</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E199" s="5" t="n">
-        <v>0.025765</v>
-      </c>
-      <c r="F199" s="5" t="n">
-        <v>0.079664</v>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Flow-through share premium liability renunciation 10,13,14</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="H199" s="5" t="n">
+        <v>2.613553</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -14421,27 +14457,31 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income tax recovery (expense)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Reorganization costs 12</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" s="5" t="n">
-        <v>0.07428999999999999</v>
+          <t>Deferred income tax recovery 13</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G200" s="5" t="n">
+        <v>0.058</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -14472,25 +14512,31 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder</t>
+          <t>Income tax recovery (expense)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Communications</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" s="5" t="n">
-        <v>0.131606</v>
-      </c>
-      <c r="F201" s="5" t="n">
-        <v>0.083131</v>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Current income tax expense 13</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G201" s="5" t="n">
+        <v>-0.03</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -14521,30 +14567,34 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder</t>
+          <t>$3,906,388          $(482,125)    LOSS (INCOME) FOR THE YEAR</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Travel and related costs</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" s="5" t="n">
-        <v>0.020108</v>
-      </c>
-      <c r="F202" s="5" t="n">
-        <v>0.047519</v>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Weighted average number of shares - basic</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G202" s="5" t="n">
+        <v>110.224168</v>
+      </c>
+      <c r="H202" s="5" t="n">
+        <v>146.238517</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -14570,34 +14620,34 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder</t>
+          <t>Loss (earnings) per share – basic                                      $0.03              $(0.01)</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Total expenses</t>
+          <t>Weighted average number of shares - diluted</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E203" s="5" t="n">
-        <v>1.111603</v>
-      </c>
-      <c r="F203" s="5" t="n">
-        <v>1.243009</v>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G203" s="5" t="n">
+        <v>124.350126</v>
+      </c>
+      <c r="H203" s="5" t="n">
+        <v>146.238517</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -14623,20 +14673,20 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Transfer agent, filing fees and shareholder</t>
+          <t>Period from</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Loss from operations for the period</t>
+          <t>February</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
       <c r="E204" s="5" t="n">
-        <v>-1.111603</v>
+        <v>0.002018</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>-1.243009</v>
+        <v>1e-06</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -14672,20 +14722,20 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>(date of</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Flow-through share premium renunciation 8,11,13</t>
+          <t>Notes October 31, 2019 October</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
       <c r="E205" s="5" t="n">
-        <v>0.009176</v>
+        <v>0.002018</v>
       </c>
       <c r="F205" s="5" t="n">
-        <v>0.093241</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -14721,24 +14771,24 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the period $</t>
+          <t>Consulting and management fees 10 $</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E206" s="5" t="n">
-        <v>-1.102427</v>
+        <v>0.16685</v>
       </c>
       <c r="F206" s="5" t="n">
-        <v>-1.149768</v>
+        <v>0.3381</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -14774,20 +14824,20 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Deferred income tax recovery</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Weighted average number of shares, basic and diluted</t>
+          <t>Exploration expense 5,10,14</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
       <c r="E207" s="5" t="n">
-        <v>26.569769</v>
+        <v>0.506012</v>
       </c>
       <c r="F207" s="5" t="n">
-        <v>35.542673</v>
+        <v>0.532691</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -14823,46 +14873,701 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Share-based payments 9</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" s="5" t="n">
+        <v>0.182262</v>
+      </c>
+      <c r="F208" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Office, rent and general</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" s="5" t="n">
+        <v>0.00471</v>
+      </c>
+      <c r="F209" s="5" t="n">
+        <v>0.041904</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="n">
+        <v>0.025765</v>
+      </c>
+      <c r="F210" s="5" t="n">
+        <v>0.079664</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Reorganization costs 12</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" s="5" t="n">
+        <v>0.07428999999999999</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Transfer agent, filing fees and shareholder</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Communications</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" s="5" t="n">
+        <v>0.131606</v>
+      </c>
+      <c r="F212" s="5" t="n">
+        <v>0.083131</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Transfer agent, filing fees and shareholder</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Travel and related costs</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" s="5" t="n">
+        <v>0.020108</v>
+      </c>
+      <c r="F213" s="5" t="n">
+        <v>0.047519</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Transfer agent, filing fees and shareholder</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="n">
+        <v>1.111603</v>
+      </c>
+      <c r="F214" s="5" t="n">
+        <v>1.243009</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Transfer agent, filing fees and shareholder</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Loss from operations for the period</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" s="5" t="n">
+        <v>-1.111603</v>
+      </c>
+      <c r="F215" s="5" t="n">
+        <v>-1.243009</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="C208" t="inlineStr">
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Flow-through share premium renunciation 8,11,13</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" s="5" t="n">
+        <v>0.009176</v>
+      </c>
+      <c r="F216" s="5" t="n">
+        <v>0.093241</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Deferred income tax recovery</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period $</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="n">
+        <v>-1.102427</v>
+      </c>
+      <c r="F217" s="5" t="n">
+        <v>-1.149768</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Deferred income tax recovery</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" s="5" t="n">
+        <v>26.569769</v>
+      </c>
+      <c r="F218" s="5" t="n">
+        <v>35.542673</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Deferred income tax recovery</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
         <is>
           <t>Loss per share, basic and diluted $</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="D219" t="inlineStr">
         <is>
           <t>BasicEPS</t>
         </is>
       </c>
-      <c r="E208" s="5" t="n">
+      <c r="E219" s="5" t="n">
         <v>-4e-08</v>
       </c>
-      <c r="F208" s="5" t="n">
+      <c r="F219" s="5" t="n">
         <v>-3e-08</v>
       </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K208" t="inlineStr">
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Share-based payments 9,10</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" s="5" t="n">
+        <v>0.182262</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Transfer agent, filing fees and shareholder</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Loss from operations for the period $</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" s="5" t="n">
+        <v>-0.605591</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
         <is>
           <t>-</t>
         </is>
